--- a/RobotOnTheFloor/RNN_Ts9/Odometry.xlsx
+++ b/RobotOnTheFloor/RNN_Ts9/Odometry.xlsx
@@ -491,22 +491,22 @@
         <v>24</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6997326480738594</v>
+        <v>0.9414170277800897</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03036511620284625</v>
+        <v>0.005924316271997679</v>
       </c>
       <c r="G2" t="n">
-        <v>-4.809086808305537</v>
+        <v>-3.246088307928199</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4627403532469549</v>
+        <v>0.3382349874199223</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.670904897704593</v>
+        <v>-0.08409441728212341</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7502942760464593</v>
+        <v>0.3045371764003038</v>
       </c>
     </row>
     <row r="3">
@@ -525,22 +525,22 @@
         <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>-4.396802844250286</v>
+        <v>-0.7989002087896979</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5457621164548743</v>
+        <v>0.181917259824704</v>
       </c>
       <c r="G3" t="n">
-        <v>-13.08059615809235</v>
+        <v>-36.55750539975347</v>
       </c>
       <c r="H3" t="n">
-        <v>1.121632410589494</v>
+        <v>2.99175651686048</v>
       </c>
       <c r="I3" t="n">
-        <v>-242.1364971059801</v>
+        <v>-60.06903086334057</v>
       </c>
       <c r="J3" t="n">
-        <v>68.30041842125516</v>
+        <v>17.15513882199513</v>
       </c>
     </row>
     <row r="4">
@@ -559,22 +559,22 @@
         <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3998824644139007</v>
+        <v>-1.259666175509125</v>
       </c>
       <c r="F4" t="n">
-        <v>0.141565819359245</v>
+        <v>0.2285131085974795</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.600474238400484</v>
+        <v>-0.5243936126934403</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2868066489472868</v>
+        <v>0.121430176911218</v>
       </c>
       <c r="I4" t="n">
-        <v>-1615.287851239928</v>
+        <v>-409.4644164068105</v>
       </c>
       <c r="J4" t="n">
-        <v>454.0377024546813</v>
+        <v>115.3051545996462</v>
       </c>
     </row>
     <row r="5">
@@ -593,22 +593,22 @@
         <v>25</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5135556518374329</v>
+        <v>0.7979829552935472</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1530612401005333</v>
+        <v>0.02042936402548327</v>
       </c>
       <c r="G5" t="n">
-        <v>-10.32953662010787</v>
+        <v>-3.885688325274776</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9024884548492846</v>
+        <v>0.3891842584035393</v>
       </c>
       <c r="I5" t="n">
-        <v>-8.616910549689784</v>
+        <v>-1.217997777986174</v>
       </c>
       <c r="J5" t="n">
-        <v>2.701523721374037</v>
+        <v>0.6230663766938996</v>
       </c>
     </row>
     <row r="6">
@@ -627,22 +627,22 @@
         <v>24</v>
       </c>
       <c r="E6" t="n">
-        <v>-20.64773498181548</v>
+        <v>-10.43602520551578</v>
       </c>
       <c r="F6" t="n">
-        <v>2.010775890262005</v>
+        <v>1.062248950432745</v>
       </c>
       <c r="G6" t="n">
-        <v>-11.18503680494425</v>
+        <v>-12.16806944304358</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6368542302053937</v>
+        <v>0.6882326957796214</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9763254573603439</v>
+        <v>-0.5536203247360083</v>
       </c>
       <c r="J6" t="n">
-        <v>5.824293224919864</v>
+        <v>4.578567916411691</v>
       </c>
     </row>
     <row r="7">
@@ -661,22 +661,22 @@
         <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.8851615610498</v>
+        <v>-31.35049645703054</v>
       </c>
       <c r="F7" t="n">
-        <v>0.360877902620945</v>
+        <v>3.004914757522963</v>
       </c>
       <c r="G7" t="n">
-        <v>-11.21131807125586</v>
+        <v>-41.05262906213212</v>
       </c>
       <c r="H7" t="n">
-        <v>0.63822782766707</v>
+        <v>2.197891983273303</v>
       </c>
       <c r="I7" t="n">
-        <v>-80.57503860755234</v>
+        <v>-23.9571451380666</v>
       </c>
       <c r="J7" t="n">
-        <v>240.4042021090635</v>
+        <v>73.54949095030553</v>
       </c>
     </row>
     <row r="8">
@@ -695,22 +695,22 @@
         <v>22</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.7254814808934</v>
+        <v>-5.441898522188013</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4389320286691338</v>
+        <v>0.5983634891507609</v>
       </c>
       <c r="G8" t="n">
-        <v>-27.30217622020803</v>
+        <v>-3.259509573516205</v>
       </c>
       <c r="H8" t="n">
-        <v>1.479220862307477</v>
+        <v>0.2226244150032814</v>
       </c>
       <c r="I8" t="n">
-        <v>-268.7711165675994</v>
+        <v>-72.95415705966786</v>
       </c>
       <c r="J8" t="n">
-        <v>795.0239575430687</v>
+        <v>217.9452247164713</v>
       </c>
     </row>
     <row r="9">
@@ -729,22 +729,22 @@
         <v>25</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.709439012985538</v>
+        <v>-7.468434665788765</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2516695002051296</v>
+        <v>0.7866007352977568</v>
       </c>
       <c r="G9" t="n">
-        <v>-21.58564855368485</v>
+        <v>-31.18674328272599</v>
       </c>
       <c r="H9" t="n">
-        <v>1.180445004278535</v>
+        <v>1.682248805996354</v>
       </c>
       <c r="I9" t="n">
-        <v>-14.85997555862938</v>
+        <v>-5.355032664330905</v>
       </c>
       <c r="J9" t="n">
-        <v>46.73984633932553</v>
+        <v>18.72848095598772</v>
       </c>
     </row>
     <row r="10">
@@ -763,22 +763,22 @@
         <v>24</v>
       </c>
       <c r="E10" t="n">
-        <v>0.07179449698528073</v>
+        <v>-1.027681283841993</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0733955323255919</v>
+        <v>0.1603338341895854</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6742840845252989</v>
+        <v>-8.482065492597604</v>
       </c>
       <c r="H10" t="n">
-        <v>0.09923718038827002</v>
+        <v>0.5620154025468672</v>
       </c>
       <c r="I10" t="n">
-        <v>-32.74866094996558</v>
+        <v>-8.870873215117326</v>
       </c>
       <c r="J10" t="n">
-        <v>13.42656034901751</v>
+        <v>3.927026174957273</v>
       </c>
     </row>
     <row r="11">
@@ -797,22 +797,22 @@
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.394492135055446</v>
+        <v>0.0946960337996946</v>
       </c>
       <c r="F11" t="n">
-        <v>0.268410989181001</v>
+        <v>0.07158465048950201</v>
       </c>
       <c r="G11" t="n">
-        <v>-37.96152346193639</v>
+        <v>-17.76564636414071</v>
       </c>
       <c r="H11" t="n">
-        <v>2.309304476898391</v>
+        <v>1.112266341508412</v>
       </c>
       <c r="I11" t="n">
-        <v>-262.9994769158232</v>
+        <v>-61.01851252381945</v>
       </c>
       <c r="J11" t="n">
-        <v>105.0294977384271</v>
+        <v>24.67343229978459</v>
       </c>
     </row>
     <row r="12">
@@ -831,22 +831,22 @@
         <v>22</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8363342002847129</v>
+        <v>-0.02787569414080138</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1452035413707834</v>
+        <v>0.08127670380209442</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.893962043392005</v>
+        <v>-0.724192306482863</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1715292141825047</v>
+        <v>0.1021953111326501</v>
       </c>
       <c r="I12" t="n">
-        <v>-2836.127691714314</v>
+        <v>-702.4643184712645</v>
       </c>
       <c r="J12" t="n">
-        <v>1128.722298853455</v>
+        <v>279.8661001495094</v>
       </c>
     </row>
     <row r="13">
@@ -865,22 +865,22 @@
         <v>25</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.915759023358776</v>
+        <v>-0.7123305416506365</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2305563638197604</v>
+        <v>0.1353982617142754</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.065695383216607</v>
+        <v>-8.946805644370549</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4780651474257077</v>
+        <v>0.5895612071695275</v>
       </c>
       <c r="I13" t="n">
-        <v>-27.15378941353415</v>
+        <v>-6.359195381859084</v>
       </c>
       <c r="J13" t="n">
-        <v>11.20069780471488</v>
+        <v>2.927780781028074</v>
       </c>
     </row>
     <row r="14">
@@ -899,22 +899,22 @@
         <v>24</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3593638290761892</v>
+        <v>0.3283561301589957</v>
       </c>
       <c r="F14" t="n">
-        <v>0.05918465834702031</v>
+        <v>0.06204927971845334</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.01013312292617941</v>
+        <v>-0.2100686674320718</v>
       </c>
       <c r="H14" t="n">
-        <v>0.07477121212130661</v>
+        <v>0.08957067040016509</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.610956565966063</v>
+        <v>-0.9980128864734561</v>
       </c>
       <c r="J14" t="n">
-        <v>1.851362874302767</v>
+        <v>0.6592542353352873</v>
       </c>
     </row>
     <row r="15">
@@ -933,22 +933,22 @@
         <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.913382677117844</v>
+        <v>-8.372776343228933</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3615347169554564</v>
+        <v>0.8658964179888787</v>
       </c>
       <c r="G15" t="n">
-        <v>-6.97577308096461</v>
+        <v>-36.29231683327141</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5903758696088159</v>
+        <v>2.760420056673348</v>
       </c>
       <c r="I15" t="n">
-        <v>-111.5616857080579</v>
+        <v>-24.98855896021432</v>
       </c>
       <c r="J15" t="n">
-        <v>37.14028500111103</v>
+        <v>8.575053584875734</v>
       </c>
     </row>
     <row r="16">
@@ -967,22 +967,22 @@
         <v>22</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.145385085361546</v>
+        <v>-0.7600983548091667</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1981996787924371</v>
+        <v>0.1626052734991791</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.021920720199164</v>
+        <v>-0.4502069890954887</v>
       </c>
       <c r="H16" t="n">
-        <v>0.297707183815481</v>
+        <v>0.1073459843464459</v>
       </c>
       <c r="I16" t="n">
-        <v>-2218.736860163318</v>
+        <v>-553.1425640034239</v>
       </c>
       <c r="J16" t="n">
-        <v>732.4131572421471</v>
+        <v>182.8420801347349</v>
       </c>
     </row>
     <row r="17">
@@ -1001,22 +1001,22 @@
         <v>25</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.139962114578553</v>
+        <v>0.8383912246370743</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1976986819902201</v>
+        <v>0.01493009697211215</v>
       </c>
       <c r="G17" t="n">
-        <v>-9.182318043226385</v>
+        <v>-0.3496593163789381</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7537068580537248</v>
+        <v>0.09990333030970432</v>
       </c>
       <c r="I17" t="n">
-        <v>-10.20197192483842</v>
+        <v>-1.526813651463074</v>
       </c>
       <c r="J17" t="n">
-        <v>3.696146048683066</v>
+        <v>0.8337346635287504</v>
       </c>
     </row>
   </sheetData>
